--- a/Feasibility Analysis.xlsx
+++ b/Feasibility Analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65D004E-28B0-4949-B73C-7550818D0922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6BE79A-9751-4622-900F-D6F62C607319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="135" windowWidth="14610" windowHeight="15480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Manual record-keeping; delays; errors; no real-time tracking.</t>
   </si>
@@ -144,12 +144,6 @@
     <t>## Summary</t>
   </si>
   <si>
-    <t>Perfect 👍 Here’s a Cost–Benefit Analysis Table for the Library Management System (LMS):</t>
-  </si>
-  <si>
-    <t>Cost–Benefit Analysis – Library Management System</t>
-  </si>
-  <si>
     <t>Proposed Solution / Benefits</t>
   </si>
   <si>
@@ -220,14 +214,26 @@
   </si>
   <si>
     <t>Conclusion: The Online Job Portal System is economically feasible, with clear cost savings and long-term value.</t>
+  </si>
+  <si>
+    <t>Cost-Benefit Analysis — Online Job Portal System</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -256,8 +262,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,7 +586,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -662,7 +669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A5:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -671,19 +678,15 @@
     <col min="4" max="4" width="80.42578125" customWidth="1"/>
     <col min="5" max="5" width="52.28515625" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -700,75 +703,75 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
         <v>56</v>
       </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
       <c r="E11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -776,16 +779,16 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -796,7 +799,7 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -809,22 +812,22 @@
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
